--- a/target/test-classes/TestData.xlsx
+++ b/target/test-classes/TestData.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Anjali Dubey\Desktop\work\aps\src\test\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\aps\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEDCF51A-DCC9-406D-991E-BE07132D7F8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90569154-0017-4913-AFDF-23B17AE2462C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FlightBookingData" sheetId="2" r:id="rId1"/>
@@ -20,25 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
-  <si>
-    <t>Username</t>
-  </si>
-  <si>
-    <t>Password</t>
-  </si>
-  <si>
-    <t>ExpectedResult</t>
-  </si>
-  <si>
-    <t>admin@example.com</t>
-  </si>
-  <si>
-    <t>Admin@123</t>
-  </si>
-  <si>
-    <t>Pass</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>FromCity</t>
   </si>
@@ -49,44 +31,60 @@
     <t>DepartDate</t>
   </si>
   <si>
-    <t>Travellers</t>
-  </si>
-  <si>
-    <t>PassengerName</t>
-  </si>
-  <si>
     <t>Mobile</t>
   </si>
   <si>
-    <t>Email</t>
-  </si>
-  <si>
-    <t>Delhi</t>
-  </si>
-  <si>
-    <t>Mumbai</t>
-  </si>
-  <si>
     <t>2026-06-15</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
     <t>Test User One</t>
   </si>
   <si>
-    <t>test1@example.com</t>
+    <t>New Delhi</t>
+  </si>
+  <si>
+    <t>Kolkata</t>
+  </si>
+  <si>
+    <t>firstName</t>
+  </si>
+  <si>
+    <t>lastName</t>
+  </si>
+  <si>
+    <t>Automation</t>
+  </si>
+  <si>
+    <t>cardNumber</t>
+  </si>
+  <si>
+    <t>cvv</t>
+  </si>
+  <si>
+    <t>exp</t>
+  </si>
+  <si>
+    <t>12/30</t>
+  </si>
+  <si>
+    <t>4111111111111111</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="17"/>
+      <color rgb="FF2A00FF"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -112,8 +110,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -416,13 +418,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="8" max="8" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="21.26953125" customWidth="1"/>
+    <col min="6" max="6" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="36.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -430,60 +434,54 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E1" t="s">
         <v>8</v>
       </c>
       <c r="F1" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="22" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" t="s">
         <v>10</v>
       </c>
-      <c r="H1" t="s">
-        <v>11</v>
-      </c>
-      <c r="I1" t="s">
-        <v>12</v>
-      </c>
-      <c r="J1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2">
+        <v>9340299487</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2">
+        <v>123</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>14</v>
-      </c>
-      <c r="E2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H2">
-        <v>9340299487</v>
-      </c>
-      <c r="I2" t="s">
-        <v>18</v>
-      </c>
-      <c r="J2" t="s">
-        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/target/test-classes/TestData.xlsx
+++ b/target/test-classes/TestData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\aps\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90569154-0017-4913-AFDF-23B17AE2462C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A76EAE1-9E0D-42C8-A3C9-3C46025CE049}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="16">
   <si>
     <t>FromCity</t>
   </si>
@@ -418,7 +418,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="4" width="21.26953125" customWidth="1"/>
@@ -484,6 +484,35 @@
         <v>14</v>
       </c>
     </row>
+    <row r="3" spans="1:9" ht="22" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F3">
+        <v>9340299487</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3">
+        <v>123</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
